--- a/space-battleship/config_excel/planet.xlsx
+++ b/space-battleship/config_excel/planet.xlsx
@@ -1371,8 +1371,10 @@
       <ns0:c r="E5">
         <ns0:v>150</ns0:v>
       </ns0:c>
-      <ns0:c r="G5" t="str">
-        <ns0:v>{"surfaceTexture":"res://assets/planets/t587e_surface.png","cloudTexture":"res://assets/planets/t587e_surface.png","radiusScale":1.05,"axisRatio":0.93,"surfaceSpeed":0.0017,"cloudSpeed":0.0022,"cloudOpacity":0.12,"shadowStrength":0.53,"glowStrength":0.38,"atmosphereColor":"e8d3a2","coronaWidth":0.035}</ns0:v>
+      <ns0:c r="G5" t="inlineStr">
+        <ns0:is>
+          <ns0:t>{"surfaceTexture":"res://assets/planets/t587e_surface.png","cloudTexture":"res://assets/planets/t587e_surface.png","radiusScale":1.05,"axisRatio":0.93,"surfaceSpeed":0.006,"cloudSpeed":0.0075,"cloudOpacity":0.12,"shadowStrength":0.53,"glowStrength":0.38,"atmosphereColor":"e8d3a2","coronaWidth":0.035}</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H5" t="n">
         <ns0:v>10</ns0:v>
@@ -1397,8 +1399,10 @@
       <ns0:c r="E6">
         <ns0:v>200</ns0:v>
       </ns0:c>
-      <ns0:c r="G6" t="str">
-        <ns0:v>{"surfaceTexture":"res://assets/planets/stellar_plasma.png","cloudOpacity":0,"shadowStrength":0,"emission":1.3,"radiusScale":0.83,"detailScale":3.2,"detailStrength":0.7,"surfaceSpeed":0.002,"cloudSpeed":0.0028,"surfaceTint":"fff4c9","shadowTint":"d49642","atmosphereColor":"ffdda0","coronaWidth":0.085,"glowStrength":0.56,"flareStrength":0.12}</ns0:v>
+      <ns0:c r="G6" t="inlineStr">
+        <ns0:is>
+          <ns0:t>{"surfaceTexture":"res://assets/planets/stellar_plasma.png","cloudOpacity":0,"shadowStrength":0,"emission":1.3,"radiusScale":0.83,"detailScale":1.2,"detailStrength":0.9,"surfaceSpeed":0.0065,"cloudSpeed":0.008,"surfaceTint":"fff4c9","shadowTint":"d49642","atmosphereColor":"ffdda0","coronaWidth":0.085,"glowStrength":0.56,"flareStrength":0.12}</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H6" t="n">
         <ns0:v>15</ns0:v>
@@ -1423,8 +1427,10 @@
       <ns0:c r="E7">
         <ns0:v>250</ns0:v>
       </ns0:c>
-      <ns0:c r="G7" t="str">
-        <ns0:v>{"surfaceTexture":"res://assets/planets/stellar_plasma.png","cloudOpacity":0,"shadowStrength":0,"emission":1.1,"radiusScale":1.22,"detailScale":0.55,"detailStrength":1,"surfaceSpeed":0.0007,"cloudSpeed":0.0011,"surfaceTint":"ff8539","shadowTint":"6b100c","atmosphereColor":"ee6333","coronaWidth":0.2,"glowStrength":0.27,"pulseStrength":0.009,"pulseSpeed":0.05}</ns0:v>
+      <ns0:c r="G7" t="inlineStr">
+        <ns0:is>
+          <ns0:t>{"surfaceTexture":"res://assets/planets/stellar_plasma.png","cloudOpacity":0,"shadowStrength":0,"emission":1.1,"radiusScale":1.22,"detailScale":0.55,"detailStrength":1,"surfaceSpeed":0.0035,"cloudSpeed":0.0045,"surfaceTint":"ff8539","shadowTint":"6b100c","atmosphereColor":"ee6333","coronaWidth":0.2,"glowStrength":0.27,"pulseStrength":0.009,"pulseSpeed":0.05}</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H7" t="n">
         <ns0:v>20</ns0:v>
@@ -1449,8 +1455,10 @@
       <ns0:c r="E8">
         <ns0:v>300</ns0:v>
       </ns0:c>
-      <ns0:c r="G8" t="str">
-        <ns0:v>{"surfaceTexture":"res://assets/planets/stellar_plasma.png","cloudOpacity":0,"shadowStrength":0,"emission":1.6,"radiusScale":0.22,"detailScale":2,"detailStrength":0.06,"surfaceSpeed":0.006,"cloudSpeed":0.009,"surfaceTint":"f6ffff","shadowTint":"a0d9ff","atmosphereColor":"96ceff","coronaWidth":0.065,"glowStrength":0.8}</ns0:v>
+      <ns0:c r="G8" t="inlineStr">
+        <ns0:is>
+          <ns0:t>{"surfaceTexture":"res://assets/planets/stellar_plasma.png","cloudOpacity":0,"shadowStrength":0,"emission":1.6,"radiusScale":0.22,"detailScale":1.0,"detailStrength":0.8,"surfaceSpeed":0.008,"cloudSpeed":0.01,"surfaceTint":"f6ffff","shadowTint":"a0d9ff","atmosphereColor":"96ceff","coronaWidth":0.065,"glowStrength":0.8}</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H8" t="n">
         <ns0:v>25</ns0:v>
@@ -1475,8 +1483,10 @@
       <ns0:c r="E9">
         <ns0:v>350</ns0:v>
       </ns0:c>
-      <ns0:c r="G9" t="str">
-        <ns0:v>{"surfaceTexture":"res://assets/planets/stellar_plasma.png","cloudOpacity":0,"shadowStrength":0,"emission":1.7,"radiusScale":0.16,"detailStrength":0.12,"surfaceSpeed":0.35,"cloudSpeed":0.42,"surfaceTint":"edffff","shadowTint":"8bc9ff","atmosphereColor":"6fbfff","coronaWidth":0.12,"glowStrength":0.8,"beamLength":7.5,"beamWidth":0.2,"beamSpeed":1.6,"magnetosphere":0.55}</ns0:v>
+      <ns0:c r="G9" t="inlineStr">
+        <ns0:is>
+          <ns0:t>{"surfaceTexture":"res://assets/planets/stellar_plasma.png","cloudOpacity":0,"shadowStrength":0,"emission":1.7,"radiusScale":0.16,"detailStrength":0.85,"surfaceSpeed":0.02,"cloudSpeed":0.025,"surfaceTint":"edffff","shadowTint":"8bc9ff","atmosphereColor":"6fbfff","coronaWidth":0.12,"glowStrength":0.8,"beamLength":7.5,"beamWidth":0.2,"beamSpeed":1.6,"magnetosphere":0.55,"detailScale":1.0}</ns0:t>
+        </ns0:is>
       </ns0:c>
       <ns0:c r="H9" t="n">
         <ns0:v>30</ns0:v>

--- a/space-battleship/config_excel/planet.xlsx
+++ b/space-battleship/config_excel/planet.xlsx
@@ -1,316 +1,187 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\放置\space-battleship\config_excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="29868" windowHeight="13380" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="planet" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="planet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>unlockId</t>
-  </si>
-  <si>
-    <t>baseTime</t>
-  </si>
-  <si>
-    <t>baseExp</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>数字ID</t>
-  </si>
-  <si>
-    <t>星球名称</t>
-  </si>
-  <si>
-    <t>解锁配置ID</t>
-  </si>
-  <si>
-    <t>探索秒数</t>
-  </si>
-  <si>
-    <t>基础经验</t>
-  </si>
-  <si>
-    <t>星球标签</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>number</t>
-  </si>
-  <si>
-    <r>
-      <t>始源星</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-E178b</t>
-    </r>
-  </si>
-  <si>
-    <t>planet/1</t>
-  </si>
-  <si>
-    <t>气态巨星-T587e</t>
-  </si>
-  <si>
-    <t>planet/2</t>
-  </si>
-  <si>
-    <t>主序星-UTE334</t>
-  </si>
-  <si>
-    <t>planet/3</t>
-  </si>
-  <si>
-    <t>红巨星-RG214</t>
-  </si>
-  <si>
-    <t>planet/4</t>
-  </si>
-  <si>
-    <t>白矮星-WS113</t>
-  </si>
-  <si>
-    <t>planet/5</t>
-  </si>
-  <si>
-    <r>
-      <t>脉冲星</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-        <charset val="134"/>
-      </rPr>
-      <t>-PSR T46+38</t>
-    </r>
-  </si>
-  <si>
-    <t>planet/6</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="22">
     <font>
-      <sz val="11"/>
       <name val="Carlito"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -610,158 +481,159 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1008,7 +880,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1017,7 +889,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1030,11 +902,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1231,272 +1166,352 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:sheetPr/>
-  <ns0:dimension ref="A1:I9"/>
-  <ns0:sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="5"/>
-  <ns0:cols>
-    <ns0:col min="2" max="2" width="13.6" customWidth="1"/>
-    <ns0:col min="3" max="3" width="10.5" customWidth="1"/>
-    <ns0:col min="6" max="6" width="24" customWidth="1"/>
-    <ns0:col min="7" max="7" width="64" customWidth="1"/>
-    <ns0:col min="8" max="8" width="23" customWidth="1"/>
-    <ns0:col min="9" max="9" width="24" customWidth="1"/>
-  </ns0:cols>
-  <ns0:sheetData>
-    <ns0:row r="1" spans="1:6">
-      <ns0:c r="A1" t="s">
-        <ns0:v>0</ns0:v>
-      </ns0:c>
-      <ns0:c r="B1" t="s">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="C1" t="s">
-        <ns0:v>2</ns0:v>
-      </ns0:c>
-      <ns0:c r="D1" t="s">
-        <ns0:v>3</ns0:v>
-      </ns0:c>
-      <ns0:c r="E1" t="s">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
-      <ns0:c r="F1" t="s">
-        <ns0:v>5</ns0:v>
-      </ns0:c>
-      <ns0:c r="G1" t="str">
-        <ns0:v>visual</ns0:v>
-      </ns0:c>
-      <ns0:c r="H1" t="str">
-        <ns0:v>reforgeStartLevel</ns0:v>
-      </ns0:c>
-      <ns0:c r="I1" t="str">
-        <ns0:v>minTime</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="2" spans="1:6">
-      <ns0:c r="A2" t="s">
-        <ns0:v>6</ns0:v>
-      </ns0:c>
-      <ns0:c r="B2" t="s">
-        <ns0:v>7</ns0:v>
-      </ns0:c>
-      <ns0:c r="C2" t="s">
-        <ns0:v>8</ns0:v>
-      </ns0:c>
-      <ns0:c r="D2" t="s">
-        <ns0:v>9</ns0:v>
-      </ns0:c>
-      <ns0:c r="E2" t="s">
-        <ns0:v>10</ns0:v>
-      </ns0:c>
-      <ns0:c r="F2" t="s">
-        <ns0:v>11</ns0:v>
-      </ns0:c>
-      <ns0:c r="G2" t="str">
-        <ns0:v>动态天体外观（JSON；缺项继承通用默认）</ns0:v>
-      </ns0:c>
-      <ns0:c r="H2" t="str">
-        <ns0:v>重铸后起始关卡</ns0:v>
-      </ns0:c>
-      <ns0:c r="I2" t="str">
-        <ns0:v>探索时间下限（秒）</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="3" spans="1:6">
-      <ns0:c r="A3" t="s">
-        <ns0:v>12</ns0:v>
-      </ns0:c>
-      <ns0:c r="B3" t="s">
-        <ns0:v>13</ns0:v>
-      </ns0:c>
-      <ns0:c r="C3" t="s">
-        <ns0:v>13</ns0:v>
-      </ns0:c>
-      <ns0:c r="D3" t="s">
-        <ns0:v>14</ns0:v>
-      </ns0:c>
-      <ns0:c r="E3" t="s">
-        <ns0:v>14</ns0:v>
-      </ns0:c>
-      <ns0:c r="F3" t="s">
-        <ns0:v>13</ns0:v>
-      </ns0:c>
-      <ns0:c r="G3" t="str">
-        <ns0:v>string</ns0:v>
-      </ns0:c>
-      <ns0:c r="H3" t="str">
-        <ns0:v>int</ns0:v>
-      </ns0:c>
-      <ns0:c r="I3" t="str">
-        <ns0:v>float</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="4" ht="14.4" spans="1:6">
-      <ns0:c r="A4">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="B4" s="1" t="s">
-        <ns0:v>15</ns0:v>
-      </ns0:c>
-      <ns0:c r="C4" t="s">
-        <ns0:v>16</ns0:v>
-      </ns0:c>
-      <ns0:c r="D4">
-        <ns0:v>60</ns0:v>
-      </ns0:c>
-      <ns0:c r="E4">
-        <ns0:v>100</ns0:v>
-      </ns0:c>
-      <ns0:c r="G4"/>
-      <ns0:c r="H4" t="n">
-        <ns0:v>5</ns0:v>
-      </ns0:c>
-      <ns0:c r="I4" t="n">
-        <ns0:v>5</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="5" customFormat="1" ht="14.4" spans="1:6">
-      <ns0:c r="A5">
-        <ns0:v>2</ns0:v>
-      </ns0:c>
-      <ns0:c r="B5" s="1" t="s">
-        <ns0:v>17</ns0:v>
-      </ns0:c>
-      <ns0:c r="C5" t="s">
-        <ns0:v>18</ns0:v>
-      </ns0:c>
-      <ns0:c r="D5">
-        <ns0:v>60</ns0:v>
-      </ns0:c>
-      <ns0:c r="E5">
-        <ns0:v>150</ns0:v>
-      </ns0:c>
-      <ns0:c r="G5" t="inlineStr">
-        <ns0:is>
-          <ns0:t>{"surfaceTexture":"res://assets/planets/t587e_surface.png","cloudTexture":"res://assets/planets/t587e_surface.png","radiusScale":1.05,"axisRatio":0.93,"surfaceSpeed":0.006,"cloudSpeed":0.0075,"cloudOpacity":0.12,"shadowStrength":0.53,"glowStrength":0.38,"atmosphereColor":"e8d3a2","coronaWidth":0.035}</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H5" t="n">
-        <ns0:v>10</ns0:v>
-      </ns0:c>
-      <ns0:c r="I5" t="n">
-        <ns0:v>5</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="6" customFormat="1" ht="14.4" spans="1:6">
-      <ns0:c r="A6">
-        <ns0:v>3</ns0:v>
-      </ns0:c>
-      <ns0:c r="B6" s="1" t="s">
-        <ns0:v>19</ns0:v>
-      </ns0:c>
-      <ns0:c r="C6" t="s">
-        <ns0:v>20</ns0:v>
-      </ns0:c>
-      <ns0:c r="D6">
-        <ns0:v>60</ns0:v>
-      </ns0:c>
-      <ns0:c r="E6">
-        <ns0:v>200</ns0:v>
-      </ns0:c>
-      <ns0:c r="G6" t="inlineStr">
-        <ns0:is>
-          <ns0:t>{"surfaceTexture":"res://assets/planets/stellar_plasma.png","cloudOpacity":0,"shadowStrength":0,"emission":1.3,"radiusScale":0.83,"detailScale":1.2,"detailStrength":0.9,"surfaceSpeed":0.0065,"cloudSpeed":0.008,"surfaceTint":"fff4c9","shadowTint":"d49642","atmosphereColor":"ffdda0","coronaWidth":0.085,"glowStrength":0.56,"flareStrength":0.12}</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H6" t="n">
-        <ns0:v>15</ns0:v>
-      </ns0:c>
-      <ns0:c r="I6" t="n">
-        <ns0:v>5</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="7" customFormat="1" ht="14.4" spans="1:6">
-      <ns0:c r="A7">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
-      <ns0:c r="B7" s="1" t="s">
-        <ns0:v>21</ns0:v>
-      </ns0:c>
-      <ns0:c r="C7" t="s">
-        <ns0:v>22</ns0:v>
-      </ns0:c>
-      <ns0:c r="D7">
-        <ns0:v>60</ns0:v>
-      </ns0:c>
-      <ns0:c r="E7">
-        <ns0:v>250</ns0:v>
-      </ns0:c>
-      <ns0:c r="G7" t="inlineStr">
-        <ns0:is>
-          <ns0:t>{"surfaceTexture":"res://assets/planets/stellar_plasma.png","cloudOpacity":0,"shadowStrength":0,"emission":1.1,"radiusScale":1.22,"detailScale":0.55,"detailStrength":1,"surfaceSpeed":0.0035,"cloudSpeed":0.0045,"surfaceTint":"ff8539","shadowTint":"6b100c","atmosphereColor":"ee6333","coronaWidth":0.2,"glowStrength":0.27,"pulseStrength":0.009,"pulseSpeed":0.05}</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H7" t="n">
-        <ns0:v>20</ns0:v>
-      </ns0:c>
-      <ns0:c r="I7" t="n">
-        <ns0:v>5</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="8" customFormat="1" ht="14.4" spans="1:6">
-      <ns0:c r="A8">
-        <ns0:v>5</ns0:v>
-      </ns0:c>
-      <ns0:c r="B8" s="1" t="s">
-        <ns0:v>23</ns0:v>
-      </ns0:c>
-      <ns0:c r="C8" t="s">
-        <ns0:v>24</ns0:v>
-      </ns0:c>
-      <ns0:c r="D8">
-        <ns0:v>60</ns0:v>
-      </ns0:c>
-      <ns0:c r="E8">
-        <ns0:v>300</ns0:v>
-      </ns0:c>
-      <ns0:c r="G8" t="inlineStr">
-        <ns0:is>
-          <ns0:t>{"surfaceTexture":"res://assets/planets/stellar_plasma.png","cloudOpacity":0,"shadowStrength":0,"emission":1.6,"radiusScale":0.22,"detailScale":1.0,"detailStrength":0.8,"surfaceSpeed":0.008,"cloudSpeed":0.01,"surfaceTint":"f6ffff","shadowTint":"a0d9ff","atmosphereColor":"96ceff","coronaWidth":0.065,"glowStrength":0.8}</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H8" t="n">
-        <ns0:v>25</ns0:v>
-      </ns0:c>
-      <ns0:c r="I8" t="n">
-        <ns0:v>5</ns0:v>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="9" customFormat="1" ht="14.4" spans="1:6">
-      <ns0:c r="A9">
-        <ns0:v>6</ns0:v>
-      </ns0:c>
-      <ns0:c r="B9" s="1" t="s">
-        <ns0:v>25</ns0:v>
-      </ns0:c>
-      <ns0:c r="C9" t="s">
-        <ns0:v>26</ns0:v>
-      </ns0:c>
-      <ns0:c r="D9">
-        <ns0:v>60</ns0:v>
-      </ns0:c>
-      <ns0:c r="E9">
-        <ns0:v>350</ns0:v>
-      </ns0:c>
-      <ns0:c r="G9" t="inlineStr">
-        <ns0:is>
-          <ns0:t>{"surfaceTexture":"res://assets/planets/stellar_plasma.png","cloudOpacity":0,"shadowStrength":0,"emission":1.7,"radiusScale":0.16,"detailStrength":0.85,"surfaceSpeed":0.02,"cloudSpeed":0.025,"surfaceTint":"edffff","shadowTint":"8bc9ff","atmosphereColor":"6fbfff","coronaWidth":0.12,"glowStrength":0.8,"beamLength":7.5,"beamWidth":0.2,"beamSpeed":1.6,"magnetosphere":0.55,"detailScale":1.0}</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H9" t="n">
-        <ns0:v>30</ns0:v>
-      </ns0:c>
-      <ns0:c r="I9" t="n">
-        <ns0:v>5</ns0:v>
-      </ns0:c>
-    </ns0:row>
-  </ns0:sheetData>
-  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ns0:headerFooter/>
-</ns0:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.8"/>
+  <cols>
+    <col width="13.6" customWidth="1" style="2" min="2" max="2"/>
+    <col width="10.5" customWidth="1" style="2" min="3" max="3"/>
+    <col width="24" customWidth="1" style="2" min="6" max="6"/>
+    <col width="64" customWidth="1" style="2" min="7" max="7"/>
+    <col width="23" customWidth="1" style="2" min="8" max="8"/>
+    <col width="24" customWidth="1" style="2" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>unlockId</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>baseTime</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>baseExp</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>visual</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>reforgeStartLevel</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>minTime</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>数字ID</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>星球名称</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>解锁配置ID</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>探索秒数</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>基础经验</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>星球标签</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>动态天体外观（JSON；缺项继承通用默认）</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>重铸后起始关卡</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>探索时间下限（秒）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.4" customHeight="1" s="2">
+      <c r="A4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>始源星-E178b</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>planet/1</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="G4" s="0" t="n"/>
+      <c r="H4" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" ht="14.4" customHeight="1" s="2">
+      <c r="A5" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>气态巨星-T587e</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>planet/2</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t>{"surfaceTexture":"res://assets/planets/t587e_surface.png","cloudTexture":"res://assets/planets/t587e_surface.png","radiusScale":1.05,"axisRatio":0.93,"surfaceSpeed":0.006,"cloudSpeed":0.0075,"cloudOpacity":0.12,"shadowStrength":0.53,"glowStrength":0.38,"atmosphereColor":"e8d3a2","coronaWidth":0.035}</t>
+        </is>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" ht="14.4" customHeight="1" s="2">
+      <c r="A6" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>主序星-UTE334</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>planet/3</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>{"surfaceTexture":"res://assets/planets/stellar_plasma.png","cloudOpacity":0,"shadowStrength":0,"emission":1.3,"radiusScale":0.83,"detailScale":1.2,"detailStrength":0.9,"surfaceSpeed":0.0065,"cloudSpeed":0.008,"surfaceTint":"fff4c9","shadowTint":"d49642","atmosphereColor":"ffdda0","coronaWidth":0.085,"glowStrength":0.56,"flareStrength":0.12}</t>
+        </is>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" ht="14.4" customHeight="1" s="2">
+      <c r="A7" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>红巨星-RG214</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>planet/4</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>{"surfaceTexture":"res://assets/planets/stellar_plasma.png","cloudOpacity":0,"shadowStrength":0,"emission":1.1,"radiusScale":1.22,"detailScale":0.55,"detailStrength":1,"surfaceSpeed":0.0035,"cloudSpeed":0.0045,"surfaceTint":"ff8539","shadowTint":"6b100c","atmosphereColor":"ee6333","coronaWidth":0.2,"glowStrength":0.27,"pulseStrength":0.009,"pulseSpeed":0.05}</t>
+        </is>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" ht="14.4" customHeight="1" s="2">
+      <c r="A8" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>白矮星-WS113</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>planet/5</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>{"surfaceTexture":"res://assets/planets/stellar_plasma.png","cloudOpacity":0,"shadowStrength":0,"emission":1.6,"radiusScale":0.22,"detailScale":1.0,"detailStrength":0.8,"surfaceSpeed":0.008,"cloudSpeed":0.01,"surfaceTint":"f6ffff","shadowTint":"a0d9ff","atmosphereColor":"96ceff","coronaWidth":0.065,"glowStrength":0.8}</t>
+        </is>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" ht="14.4" customHeight="1" s="2">
+      <c r="A9" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>脉冲星-PSR T46+38</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>planet/6</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>350</v>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>{"surfaceTexture":"res://assets/planets/stellar_plasma.png","cloudOpacity":0,"shadowStrength":0,"emission":1.7,"radiusScale":0.16,"detailStrength":0.85,"surfaceSpeed":0.02,"cloudSpeed":0.025,"surfaceTint":"edffff","shadowTint":"8bc9ff","atmosphereColor":"6fbfff","coronaWidth":0.12,"glowStrength":0.8,"beamLength":7.5,"beamWidth":0.2,"beamSpeed":1.6,"magnetosphere":0.55,"detailScale":1.0}</t>
+        </is>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>